--- a/TeplosilaWeb/Content/templates/templateTRV.xlsx
+++ b/TeplosilaWeb/Content/templates/templateTRV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pge27\OneDrive\Рабочий стол\TeploSilaWeb\TeplosilaWeb\Content\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user29\Documents\ТЗ программа подбора TRV, RDT\templateRDT,TRV (действ)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5534049D-B1CC-4712-A875-0A475055F18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B540E646-FFD3-4403-BE73-F9EE3B4C46DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10785" yWindow="765" windowWidth="15840" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="77">
   <si>
     <t>Марка регулирующего клапана</t>
   </si>
@@ -285,9 +285,6 @@
   </si>
   <si>
     <t>Потери давления на регулируемом участке (без учета регулирующего клапана) ΔPру'=</t>
-  </si>
-  <si>
-    <t>Рекомендуемая скорость управления для электропривода TW5000 - 2 сек/мм (30 мм/мин).</t>
   </si>
   <si>
     <t>Рекомендуемая скорость управления для электроприводов TSL:
@@ -610,6 +607,99 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -645,99 +735,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -761,13 +758,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>476251</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>787541</xdr:rowOff>
     </xdr:to>
@@ -799,8 +796,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1" y="0"/>
-          <a:ext cx="7067550" cy="787541"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7127875" cy="787541"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1075,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W76"/>
+  <dimension ref="A1:W75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="3" customWidth="1"/>
@@ -1093,17 +1090,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23"/>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="A1" s="54"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
@@ -1113,12 +1110,12 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="51"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="27"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1136,16 +1133,16 @@
       <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="20"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -1160,21 +1157,21 @@
       <c r="W3" s="2"/>
     </row>
     <row r="4" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="26" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -1189,21 +1186,21 @@
       <c r="W4" s="2"/>
     </row>
     <row r="5" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="26" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -1218,19 +1215,19 @@
       <c r="W5" s="2"/>
     </row>
     <row r="6" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="39"/>
+      <c r="A6" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="20"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -1245,12 +1242,12 @@
       <c r="W6" s="2"/>
     </row>
     <row r="7" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -1272,19 +1269,19 @@
       <c r="W7" s="2"/>
     </row>
     <row r="8" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -1299,19 +1296,19 @@
       <c r="W8" s="2"/>
     </row>
     <row r="9" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="21"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="50"/>
+      <c r="K9" s="52"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -1326,17 +1323,17 @@
       <c r="W9" s="2"/>
     </row>
     <row r="10" spans="1:23" s="1" customFormat="1" ht="0.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="22"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="53"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -1351,17 +1348,17 @@
       <c r="W10" s="2"/>
     </row>
     <row r="11" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="33"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="15"/>
       <c r="J11" s="11"/>
       <c r="K11" s="4"/>
       <c r="L11" s="2"/>
@@ -1378,17 +1375,17 @@
       <c r="W11" s="2"/>
     </row>
     <row r="12" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="33"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
       <c r="J12" s="11"/>
       <c r="K12" s="4" t="s">
         <v>35</v>
@@ -1407,21 +1404,21 @@
       <c r="W12" s="2"/>
     </row>
     <row r="13" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="36"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="52" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="52" t="s">
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="54"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="23"/>
       <c r="L13" s="2"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -1436,26 +1433,26 @@
       <c r="W13" s="5"/>
     </row>
     <row r="14" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="31"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="37"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="36"/>
-      <c r="J14" s="37"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="17"/>
       <c r="K14" s="4" t="s">
         <v>35</v>
       </c>
@@ -1473,24 +1470,24 @@
       <c r="W14" s="5"/>
     </row>
     <row r="15" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="31"/>
-      <c r="B15" s="31" t="s">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="31"/>
+      <c r="C15" s="18"/>
       <c r="D15" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="37"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="36"/>
-      <c r="J15" s="37"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="17"/>
       <c r="K15" s="4" t="s">
         <v>35</v>
       </c>
@@ -1508,26 +1505,26 @@
       <c r="W15" s="5"/>
     </row>
     <row r="16" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="31"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="37"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="36"/>
-      <c r="J16" s="37"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="17"/>
       <c r="K16" s="4" t="s">
         <v>35</v>
       </c>
@@ -1545,24 +1542,24 @@
       <c r="W16" s="5"/>
     </row>
     <row r="17" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="31"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="37"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="17"/>
       <c r="G17" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="36"/>
-      <c r="J17" s="37"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="17"/>
       <c r="K17" s="4" t="s">
         <v>35</v>
       </c>
@@ -1580,20 +1577,20 @@
       <c r="W17" s="5"/>
     </row>
     <row r="18" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="32" t="s">
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="33"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="37"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="17"/>
       <c r="K18" s="4"/>
       <c r="L18" s="2"/>
       <c r="M18" s="5"/>
@@ -1609,20 +1606,20 @@
       <c r="W18" s="5"/>
     </row>
     <row r="19" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31" t="s">
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="31"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
       <c r="K19" s="4"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -1638,13 +1635,13 @@
       <c r="W19" s="2"/>
     </row>
     <row r="20" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -1665,19 +1662,19 @@
       <c r="W20" s="2"/>
     </row>
     <row r="21" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="37"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="17"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -1692,21 +1689,21 @@
       <c r="W21" s="2"/>
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="33"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="32" t="s">
+      <c r="B22" s="15"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="37"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="17"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -1721,21 +1718,21 @@
       <c r="W22" s="2"/>
     </row>
     <row r="23" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="37"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="17"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -1750,13 +1747,13 @@
       <c r="W23" s="2"/>
     </row>
     <row r="24" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="34" t="s">
+      <c r="A24" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -1777,21 +1774,21 @@
       <c r="W24" s="2"/>
     </row>
     <row r="25" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="35"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="39"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="20"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -1806,21 +1803,21 @@
       <c r="W25" s="2"/>
     </row>
     <row r="26" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="35"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="39"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="20"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -1859,7 +1856,7 @@
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
     </row>
-    <row r="28" spans="1:23" s="1" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" s="1" customFormat="1" ht="73.150000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>0</v>
       </c>
@@ -1869,21 +1866,21 @@
       <c r="C28" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="30"/>
+      <c r="E28" s="43"/>
       <c r="F28" s="12" t="s">
         <v>5</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>2</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J28" s="12" t="s">
         <v>64</v>
@@ -1908,8 +1905,8 @@
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="30"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="43"/>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
@@ -1930,13 +1927,13 @@
       <c r="W29" s="2"/>
     </row>
     <row r="30" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="34" t="s">
+      <c r="A30" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -1957,33 +1954,33 @@
       <c r="W30" s="2"/>
     </row>
     <row r="31" spans="1:23" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="30"/>
-      <c r="E31" s="27" t="s">
+      <c r="D31" s="43"/>
+      <c r="E31" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="29" t="s">
+      <c r="G31" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="H31" s="30"/>
-      <c r="I31" s="27" t="s">
+      <c r="H31" s="43"/>
+      <c r="I31" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="J31" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="K31" s="27" t="s">
+      <c r="J31" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="K31" s="35" t="s">
         <v>49</v>
       </c>
       <c r="L31" s="2"/>
@@ -2000,25 +1997,25 @@
       <c r="W31" s="2"/>
     </row>
     <row r="32" spans="1:23" s="1" customFormat="1" ht="42.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="28"/>
+      <c r="A32" s="36"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="12" t="s">
         <v>48</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
       <c r="G32" s="12" t="s">
         <v>47</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -2057,20 +2054,20 @@
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
     </row>
-    <row r="34" spans="1:23" s="1" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="40" t="s">
+    <row r="34" spans="1:23" s="1" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="40"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="38"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -2085,19 +2082,19 @@
       <c r="W34" s="2"/>
     </row>
     <row r="35" spans="1:23" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="41"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
+      <c r="A35" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="39"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -2111,20 +2108,20 @@
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
     </row>
-    <row r="36" spans="1:23" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="41"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
+    <row r="36" spans="1:23" s="1" customFormat="1" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -2138,20 +2135,12 @@
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
     </row>
-    <row r="37" spans="1:23" s="1" customFormat="1" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
+    <row r="37" spans="1:23" s="1" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -2165,9 +2154,18 @@
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
     </row>
-    <row r="38" spans="1:23" s="1" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
+      <c r="D38" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" s="14"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
@@ -2187,11 +2185,11 @@
     <row r="39" spans="1:23" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
-      <c r="D39" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" s="35"/>
-      <c r="F39" s="33"/>
+      <c r="D39" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="14"/>
+      <c r="F39" s="15"/>
       <c r="G39" s="11"/>
       <c r="H39" s="4" t="s">
         <v>36</v>
@@ -2215,11 +2213,11 @@
     <row r="40" spans="1:23" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
-      <c r="D40" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="E40" s="35"/>
-      <c r="F40" s="33"/>
+      <c r="D40" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="14"/>
+      <c r="F40" s="15"/>
       <c r="G40" s="11"/>
       <c r="H40" s="4" t="s">
         <v>36</v>
@@ -2240,17 +2238,18 @@
       <c r="V40" s="2"/>
       <c r="W40" s="2"/>
     </row>
-    <row r="41" spans="1:23" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
-      <c r="D41" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="E41" s="35"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="32"/>
       <c r="F41" s="33"/>
       <c r="G41" s="11"/>
       <c r="H41" s="4" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
@@ -2268,19 +2267,15 @@
       <c r="V41" s="2"/>
       <c r="W41" s="2"/>
     </row>
-    <row r="42" spans="1:23" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="E42" s="45"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="4" t="s">
-        <v>51</v>
-      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -2322,7 +2317,7 @@
       <c r="V43" s="2"/>
       <c r="W43" s="2"/>
     </row>
-    <row r="44" spans="1:23" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2337,17 +2332,12 @@
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="2"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="2"/>
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
       <c r="W44" s="2"/>
     </row>
-    <row r="45" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2358,10 +2348,6 @@
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
@@ -2410,6 +2396,10 @@
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
@@ -2426,6 +2416,11 @@
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
@@ -2860,7 +2855,7 @@
       <c r="V66" s="2"/>
       <c r="W66" s="2"/>
     </row>
-    <row r="67" spans="1:23" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -2985,7 +2980,7 @@
       <c r="V71" s="2"/>
       <c r="W71" s="2"/>
     </row>
-    <row r="72" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:23" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -3085,39 +3080,74 @@
       <c r="V75" s="2"/>
       <c r="W75" s="2"/>
     </row>
-    <row r="76" spans="1:23" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" s="2"/>
-      <c r="Q76" s="2"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="2"/>
-      <c r="T76" s="2"/>
-      <c r="U76" s="2"/>
-      <c r="V76" s="2"/>
-      <c r="W76" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="85">
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E14:F14"/>
+  <mergeCells count="84">
+    <mergeCell ref="A9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="F4:I4"/>
     <mergeCell ref="J26:K26"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="D13:G13"/>
@@ -3130,73 +3160,12 @@
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A16:A17"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="A9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E14:F14"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/TeplosilaWeb/Content/templates/templateTRV.xlsx
+++ b/TeplosilaWeb/Content/templates/templateTRV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user29\Documents\ТЗ программа подбора TRV, RDT\templateRDT,TRV (действ)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/22451d98f477d1d3/Рабочий стол/TeploSilaWeb/TeplosilaWeb/Content/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B540E646-FFD3-4403-BE73-F9EE3B4C46DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{B540E646-FFD3-4403-BE73-F9EE3B4C46DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{482C6907-E163-4256-9CFB-1682E0CB980D}"/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="765" windowWidth="15840" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -607,30 +610,123 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -642,99 +738,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -763,8 +766,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>787541</xdr:rowOff>
     </xdr:to>
@@ -797,7 +800,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7127875" cy="787541"/>
+          <a:ext cx="7105650" cy="787541"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1090,17 +1093,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54"/>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
+      <c r="A1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
@@ -1110,12 +1113,12 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="25"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="27"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="51"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1133,16 +1136,16 @@
       <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="20"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="39"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -1157,21 +1160,21 @@
       <c r="W3" s="2"/>
     </row>
     <row r="4" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="30" t="s">
+      <c r="B4" s="26"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -1186,21 +1189,21 @@
       <c r="W4" s="2"/>
     </row>
     <row r="5" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="30" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -1215,19 +1218,19 @@
       <c r="W5" s="2"/>
     </row>
     <row r="6" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="20"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="39"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -1242,12 +1245,12 @@
       <c r="W6" s="2"/>
     </row>
     <row r="7" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -1269,19 +1272,19 @@
       <c r="W7" s="2"/>
     </row>
     <row r="8" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -1296,19 +1299,19 @@
       <c r="W8" s="2"/>
     </row>
     <row r="9" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="52"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="21"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -1323,17 +1326,17 @@
       <c r="W9" s="2"/>
     </row>
     <row r="10" spans="1:23" s="1" customFormat="1" ht="0.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="47"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="53"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="22"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -1348,17 +1351,17 @@
       <c r="W10" s="2"/>
     </row>
     <row r="11" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="11"/>
       <c r="K11" s="4"/>
       <c r="L11" s="2"/>
@@ -1375,17 +1378,17 @@
       <c r="W11" s="2"/>
     </row>
     <row r="12" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="33"/>
       <c r="J12" s="11"/>
       <c r="K12" s="4" t="s">
         <v>35</v>
@@ -1404,21 +1407,21 @@
       <c r="W12" s="2"/>
     </row>
     <row r="13" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="16"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="21" t="s">
+      <c r="A13" s="36"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="21" t="s">
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="23"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="54"/>
       <c r="L13" s="2"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -1433,26 +1436,26 @@
       <c r="W13" s="5"/>
     </row>
     <row r="14" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="18"/>
+      <c r="C14" s="31"/>
       <c r="D14" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="17"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="37"/>
       <c r="G14" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="16"/>
-      <c r="J14" s="17"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="37"/>
       <c r="K14" s="4" t="s">
         <v>35</v>
       </c>
@@ -1470,24 +1473,24 @@
       <c r="W14" s="5"/>
     </row>
     <row r="15" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18" t="s">
+      <c r="A15" s="31"/>
+      <c r="B15" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="18"/>
+      <c r="C15" s="31"/>
       <c r="D15" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="37"/>
       <c r="G15" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="16"/>
-      <c r="J15" s="17"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="37"/>
       <c r="K15" s="4" t="s">
         <v>35</v>
       </c>
@@ -1505,26 +1508,26 @@
       <c r="W15" s="5"/>
     </row>
     <row r="16" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="18"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="17"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="37"/>
       <c r="G16" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="16"/>
-      <c r="J16" s="17"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="37"/>
       <c r="K16" s="4" t="s">
         <v>35</v>
       </c>
@@ -1542,24 +1545,24 @@
       <c r="W16" s="5"/>
     </row>
     <row r="17" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18" t="s">
+      <c r="A17" s="31"/>
+      <c r="B17" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="18"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="17"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="37"/>
       <c r="G17" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="17"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="37"/>
       <c r="K17" s="4" t="s">
         <v>35</v>
       </c>
@@ -1577,20 +1580,20 @@
       <c r="W17" s="5"/>
     </row>
     <row r="18" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="13" t="s">
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="17"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="37"/>
       <c r="K18" s="4"/>
       <c r="L18" s="2"/>
       <c r="M18" s="5"/>
@@ -1606,20 +1609,20 @@
       <c r="W18" s="5"/>
     </row>
     <row r="19" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18" t="s">
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
       <c r="K19" s="4"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -1635,13 +1638,13 @@
       <c r="W19" s="2"/>
     </row>
     <row r="20" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -1662,19 +1665,19 @@
       <c r="W20" s="2"/>
     </row>
     <row r="21" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="17"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="37"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -1689,21 +1692,21 @@
       <c r="W21" s="2"/>
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="13" t="s">
+      <c r="B22" s="33"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="17"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="37"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -1718,21 +1721,21 @@
       <c r="W22" s="2"/>
     </row>
     <row r="23" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="13" t="s">
+      <c r="B23" s="33"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="17"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="37"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -1747,13 +1750,13 @@
       <c r="W23" s="2"/>
     </row>
     <row r="24" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -1774,21 +1777,21 @@
       <c r="W24" s="2"/>
     </row>
     <row r="25" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="13" t="s">
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="20"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="39"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -1803,21 +1806,21 @@
       <c r="W25" s="2"/>
     </row>
     <row r="26" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="13" t="s">
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="20"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="39"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -1866,10 +1869,10 @@
       <c r="C28" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="42" t="s">
+      <c r="D28" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="43"/>
+      <c r="E28" s="30"/>
       <c r="F28" s="12" t="s">
         <v>5</v>
       </c>
@@ -1905,8 +1908,8 @@
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="43"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="30"/>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
@@ -1927,13 +1930,13 @@
       <c r="W29" s="2"/>
     </row>
     <row r="30" spans="1:23" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -1954,33 +1957,33 @@
       <c r="W30" s="2"/>
     </row>
     <row r="31" spans="1:23" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="42" t="s">
+      <c r="C31" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="43"/>
-      <c r="E31" s="35" t="s">
+      <c r="D31" s="30"/>
+      <c r="E31" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="35" t="s">
+      <c r="F31" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="42" t="s">
+      <c r="G31" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="H31" s="43"/>
-      <c r="I31" s="35" t="s">
+      <c r="H31" s="30"/>
+      <c r="I31" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="J31" s="35" t="s">
+      <c r="J31" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="K31" s="35" t="s">
+      <c r="K31" s="27" t="s">
         <v>49</v>
       </c>
       <c r="L31" s="2"/>
@@ -1997,25 +2000,25 @@
       <c r="W31" s="2"/>
     </row>
     <row r="32" spans="1:23" s="1" customFormat="1" ht="42.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="36"/>
-      <c r="B32" s="36"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="28"/>
       <c r="C32" s="12" t="s">
         <v>48</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
       <c r="G32" s="12" t="s">
         <v>47</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -2055,19 +2058,19 @@
       <c r="W33" s="2"/>
     </row>
     <row r="34" spans="1:23" s="1" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="38" t="s">
+      <c r="A34" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="38"/>
-      <c r="K34" s="38"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -2082,19 +2085,19 @@
       <c r="W34" s="2"/>
     </row>
     <row r="35" spans="1:23" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="39" t="s">
+      <c r="A35" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="39"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -2109,19 +2112,19 @@
       <c r="W35" s="2"/>
     </row>
     <row r="36" spans="1:23" s="1" customFormat="1" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="55" t="s">
+      <c r="A36" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="55"/>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -2157,11 +2160,11 @@
     <row r="38" spans="1:23" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E38" s="14"/>
-      <c r="F38" s="15"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="33"/>
       <c r="G38" s="11"/>
       <c r="H38" s="4" t="s">
         <v>36</v>
@@ -2185,11 +2188,11 @@
     <row r="39" spans="1:23" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="14"/>
-      <c r="F39" s="15"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="33"/>
       <c r="G39" s="11"/>
       <c r="H39" s="4" t="s">
         <v>36</v>
@@ -2213,11 +2216,11 @@
     <row r="40" spans="1:23" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="E40" s="14"/>
-      <c r="F40" s="15"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="33"/>
       <c r="G40" s="11"/>
       <c r="H40" s="4" t="s">
         <v>36</v>
@@ -2242,11 +2245,11 @@
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="6"/>
-      <c r="D41" s="31" t="s">
+      <c r="D41" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="32"/>
-      <c r="F41" s="33"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="46"/>
       <c r="G41" s="11"/>
       <c r="H41" s="4" t="s">
         <v>51</v>
@@ -3082,6 +3085,74 @@
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A9:I10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
@@ -3098,74 +3169,6 @@
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E14:F14"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
